--- a/random_farmers_master.xlsx
+++ b/random_farmers_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,34 +446,29 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>land_area</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>main_crop</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>land_size</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tractor_sn</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>joined_at</t>
+          <t>serial_number</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>+84-844-9868</t>
+          <t>+84-262-8618</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,34 +476,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>3991</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>커피</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1082</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>SN-2025-1738-0001</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>최민수22</t>
+          <t>최민수78</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>010-6605-6011</t>
+          <t>010-9834-4629</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -516,34 +506,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3030</v>
+      <c r="D3" t="n">
+        <v>2993</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>SN-2025-1738-0002</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nguyen Van A</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+84-752-2659</t>
+          <t>+84-282-8104</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -551,34 +536,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>쌀</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2478</v>
+      <c r="D4" t="n">
+        <v>3864</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>SN-2025-1738-0003</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+62-765-1905</t>
+          <t>+62-512-1340</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -586,34 +566,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3731</v>
+      <c r="D5" t="n">
+        <v>3171</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>SN-2025-1738-0004</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>정우성76</t>
+          <t>박지성13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>010-9096-6440</t>
+          <t>010-9081-4707</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -621,34 +596,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3446</v>
+      <c r="D6" t="n">
+        <v>4270</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>SN-2025-1738-0005</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>정우성29</t>
+          <t>김철수7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>010-7912-2086</t>
+          <t>010-4419-3303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -656,22 +626,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>벼</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4811</v>
+      <c r="D7" t="n">
+        <v>4552</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>사과</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>SN-2025-1738-0006</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -683,7 +648,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+62-403-6212</t>
+          <t>+62-450-1588</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -691,34 +656,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4735</v>
+      <c r="D8" t="n">
+        <v>3176</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>SN-2025-1738-0007</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>박지성6</t>
+          <t>박지성65</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>010-8966-1081</t>
+          <t>010-9956-7149</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -726,34 +686,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2207</v>
+      <c r="D9" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>SN-2025-1738-0008</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+62-642-6131</t>
+          <t>+62-833-9073</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -761,34 +716,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1614</v>
+      <c r="D10" t="n">
+        <v>4844</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>SN-2025-1738-0009</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>박지성62</t>
+          <t>김철수70</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>010-9018-7646</t>
+          <t>010-1486-2199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -796,34 +746,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>2793</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>배추</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>3590</v>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>SN-2025-1738-0010</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+62-798-1200</t>
+          <t>+62-514-7187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -831,34 +776,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>카카오</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1122</v>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>SN-2025-1738-0011</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>최민수7</t>
+          <t>김철수54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>010-5967-4091</t>
+          <t>010-7203-3470</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -866,34 +806,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>배추</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2770</v>
+      <c r="D13" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>사과</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>SN-2025-1738-0012</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+62-413-6538</t>
+          <t>+62-612-8250</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -901,22 +836,17 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3939</v>
+      <c r="D14" t="n">
+        <v>2508</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>팜유</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>SN-2025-1738-0013</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -928,7 +858,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+84-986-8160</t>
+          <t>+84-983-7617</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -936,34 +866,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>쌀</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2749</v>
+      <c r="D15" t="n">
+        <v>3591</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>고무</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>SN-2025-1738-0014</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+62-338-1167</t>
+          <t>+62-278-1841</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -971,34 +896,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4052</v>
+      <c r="D16" t="n">
+        <v>4462</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>SN-2025-1738-0015</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Siti</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+62-649-9468</t>
+          <t>+62-437-4103</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1006,34 +926,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2230</v>
+      <c r="D17" t="n">
+        <v>3765</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>SN-2025-1738-0016</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+62-273-9634</t>
+          <t>+62-854-3369</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1041,34 +956,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2048</v>
+      <c r="D18" t="n">
+        <v>3691</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>팜유</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>SN-2025-1738-0017</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+84-804-3655</t>
+          <t>+84-904-2377</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1076,34 +986,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>2699</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1623</v>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>SN-2025-1738-0018</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>박지성60</t>
+          <t>최민수22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>010-7144-9277</t>
+          <t>010-8381-2852</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1111,22 +1016,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1489</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>사과</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>4799</v>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>SN-2025-1738-0019</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1038,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+62-123-5374</t>
+          <t>+62-951-5071</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1146,22 +1046,17 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1209</v>
+      <c r="D21" t="n">
+        <v>2913</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>SN-2025-1738-0020</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1068,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+84-230-7081</t>
+          <t>+84-746-9711</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1181,34 +1076,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>고무</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>3128</v>
+      <c r="D22" t="n">
+        <v>4711</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>SN-2025-1738-0021</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>김철수13</t>
+          <t>정우성68</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>010-9007-1494</t>
+          <t>010-7677-3044</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1216,34 +1106,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>인삼</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>2168</v>
+      <c r="D23" t="n">
+        <v>3929</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>SN-2025-1738-0022</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>정우성67</t>
+          <t>강호동95</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>010-8532-6555</t>
+          <t>010-7688-7465</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1251,34 +1136,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>4247</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>배추</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>3576</v>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>SN-2025-1738-0023</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>김철수8</t>
+          <t>박지성13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>010-1465-9649</t>
+          <t>010-5155-8222</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1286,34 +1166,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>배추</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>4201</v>
+      <c r="D25" t="n">
+        <v>2828</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>SN-2025-1738-0024</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Siti</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>+62-208-1130</t>
+          <t>+62-348-3608</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1321,34 +1196,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>2580</v>
+      <c r="D26" t="n">
+        <v>2119</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>SN-2025-1738-0025</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>+62-361-2017</t>
+          <t>+62-668-3758</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1356,34 +1226,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1452</v>
+      <c r="D27" t="n">
+        <v>3485</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>SN-2025-1738-0026</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>+62-903-1999</t>
+          <t>+62-688-5226</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1391,34 +1256,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>3019</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>카사바</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>3340</v>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>SN-2025-1738-0027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>최민수79</t>
+          <t>최민수55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>010-6393-6049</t>
+          <t>010-3617-4109</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1426,34 +1286,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>2559</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>인삼</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>4415</v>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>SN-2025-1738-0028</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>+62-735-9950</t>
+          <t>+62-841-5905</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1461,34 +1316,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1056</v>
+      <c r="D30" t="n">
+        <v>4259</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>SN-2025-1738-0029</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>+84-519-7510</t>
+          <t>+84-326-4080</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1496,22 +1346,17 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>3690</v>
+      <c r="D31" t="n">
+        <v>3386</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>SN-2025-1738-0030</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1368,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>+84-274-2720</t>
+          <t>+84-353-3481</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1531,34 +1376,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>4374</v>
+      <c r="D32" t="n">
+        <v>4370</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>SN-2025-1738-0031</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>강호동22</t>
+          <t>김철수35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>010-5932-6939</t>
+          <t>010-3584-8686</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1566,34 +1406,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>벼</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1968</v>
+      <c r="D33" t="n">
+        <v>1198</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>SN-2025-1738-0032</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>+62-766-1405</t>
+          <t>+62-485-1981</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1601,34 +1436,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>1799</v>
+      <c r="D34" t="n">
+        <v>4537</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>SN-2025-1738-0033</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>+62-473-3731</t>
+          <t>+62-609-6385</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1636,34 +1466,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>2742</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>카사바</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>3338</v>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>SN-2025-1738-0034</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>+62-150-9282</t>
+          <t>+62-160-8146</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1671,34 +1496,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>2988</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>팜유</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>4011</v>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>SN-2025-1738-0035</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>+84-904-4675</t>
+          <t>+84-636-4631</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1706,34 +1526,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>3188</v>
+      <c r="D37" t="n">
+        <v>4018</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>SN-2025-1738-0036</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>+62-808-5485</t>
+          <t>+62-420-8566</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1741,22 +1556,17 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>3221</v>
+      <c r="D38" t="n">
+        <v>4719</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>SN-2025-1738-0037</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1578,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>+62-598-8841</t>
+          <t>+62-783-9391</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1776,34 +1586,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>4539</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>옥수수</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>3383</v>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>SN-2025-1738-0038</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>+84-367-8259</t>
+          <t>+84-167-7732</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1811,34 +1616,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2344</v>
+      <c r="D40" t="n">
+        <v>4960</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>SN-2025-1738-0039</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>+62-549-5851</t>
+          <t>+62-521-3466</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1846,34 +1646,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4698</v>
+      <c r="D41" t="n">
+        <v>4338</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>SN-2025-1738-0040</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>강호동9</t>
+          <t>강호동42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>010-6227-9368</t>
+          <t>010-6930-5470</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1881,34 +1676,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>배추</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1914</v>
+      <c r="D42" t="n">
+        <v>2183</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>사과</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>SN-2025-1738-0041</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>김철수50</t>
+          <t>김철수74</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>010-2268-4842</t>
+          <t>010-1272-8008</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1916,34 +1706,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>배추</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1522</v>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>SN-2025-1738-0042</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>+84-399-2098</t>
+          <t>+84-678-8028</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1951,34 +1736,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1439</v>
+      <c r="D44" t="n">
+        <v>4372</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>SN-2025-1738-0043</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>+62-834-1521</t>
+          <t>+62-946-1074</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1986,34 +1766,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>3082</v>
+      <c r="D45" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>SN-2025-1738-0044</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Pham Van D</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>+84-565-8908</t>
+          <t>+84-943-5996</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2021,34 +1796,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>4005</v>
+      <c r="D46" t="n">
+        <v>2392</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>SN-2025-1738-0045</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>+62-827-2063</t>
+          <t>+62-664-7978</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2056,34 +1826,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1880</v>
+      <c r="D47" t="n">
+        <v>2307</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>SN-2025-1738-0046</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>+84-174-2691</t>
+          <t>+84-400-2602</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2091,22 +1856,17 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>4678</v>
+      <c r="D48" t="n">
+        <v>3678</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>SN-2025-1738-0047</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2118,7 +1878,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>+62-685-7649</t>
+          <t>+62-585-9693</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2126,34 +1886,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>3975</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>옥수수</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>3152</v>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>SN-2025-1738-0048</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>+62-878-6177</t>
+          <t>+62-428-9781</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2161,22 +1916,17 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>2202</v>
+      <c r="D50" t="n">
+        <v>2720</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>팜유</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>SN-2025-1738-0049</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2188,7 +1938,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>+84-610-6996</t>
+          <t>+84-921-2655</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2196,34 +1946,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>4109</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>2763</v>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>SN-2025-1738-0050</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nguyen Van A</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>+84-404-7000</t>
+          <t>+84-941-7145</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2231,34 +1976,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>4503</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>1615</v>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>SN-2025-1738-0051</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>+62-304-9670</t>
+          <t>+62-534-8849</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2266,34 +2006,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>옥수수</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>3722</v>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>SN-2025-1738-0052</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>+62-721-4165</t>
+          <t>+62-337-1832</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2301,34 +2036,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>3659</v>
+      <c r="D54" t="n">
+        <v>1767</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>SN-2025-1738-0053</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>+84-206-7852</t>
+          <t>+84-914-5546</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2336,34 +2066,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>고무</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>4039</v>
+      <c r="D55" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>SN-2025-1738-0054</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Pham Van D</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>+84-412-1552</t>
+          <t>+84-693-3957</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2371,34 +2096,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>고무</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>2426</v>
+      <c r="D56" t="n">
+        <v>4222</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>SN-2025-1738-0055</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>+84-130-2744</t>
+          <t>+84-908-2634</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2406,22 +2126,17 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>쌀</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1902</v>
+      <c r="D57" t="n">
+        <v>4140</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>SN-2025-1738-0056</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2148,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>+84-363-4300</t>
+          <t>+84-337-4217</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2441,34 +2156,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>2983</v>
+      <c r="D58" t="n">
+        <v>1949</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>고무</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>SN-2025-1738-0057</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Pham Van D</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>+84-517-1280</t>
+          <t>+84-880-4527</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2476,34 +2186,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>4117</v>
+      <c r="D59" t="n">
+        <v>1667</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>SN-2025-1738-0058</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>강호동59</t>
+          <t>강호동48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>010-6466-5405</t>
+          <t>010-3803-9589</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2511,34 +2216,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>인삼</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1016</v>
+      <c r="D60" t="n">
+        <v>3233</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>SN-2025-1738-0059</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>정우성7</t>
+          <t>박지성75</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>010-4029-9194</t>
+          <t>010-9451-4036</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2546,34 +2246,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>벼</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1643</v>
+      <c r="D61" t="n">
+        <v>2811</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>인삼</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>SN-2025-1738-0060</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Pham Van D</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>+84-632-9661</t>
+          <t>+84-318-5463</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2581,34 +2276,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>쌀</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>3321</v>
+      <c r="D62" t="n">
+        <v>1553</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>SN-2025-1738-0061</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>+62-884-5935</t>
+          <t>+62-957-2215</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2616,34 +2306,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>3734</v>
+      <c r="D63" t="n">
+        <v>2646</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>SN-2025-1738-0062</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tran Thi B</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>+84-955-8621</t>
+          <t>+84-373-2787</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2651,34 +2336,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>3603</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>용과</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>3168</v>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>SN-2025-1738-0063</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>+84-241-5090</t>
+          <t>+84-648-4367</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2686,34 +2366,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>2845</v>
+      <c r="D65" t="n">
+        <v>2786</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>SN-2025-1738-0064</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>+62-321-3394</t>
+          <t>+62-621-8711</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2721,22 +2396,17 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>카사바</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>3351</v>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>SN-2025-1738-0065</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2418,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>+84-723-8303</t>
+          <t>+84-343-1744</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2756,34 +2426,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>4748</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>4208</v>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>SN-2025-1738-0066</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>+62-479-7112</t>
+          <t>+62-731-4195</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2791,34 +2456,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>4692</v>
+      <c r="D68" t="n">
+        <v>3071</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>SN-2025-1738-0067</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>+84-810-5261</t>
+          <t>+84-534-3567</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2826,34 +2486,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1867</v>
+      <c r="D69" t="n">
+        <v>2659</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>SN-2025-1738-0068</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>이영희44</t>
+          <t>박지성81</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>010-6709-9763</t>
+          <t>010-6060-3275</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2861,22 +2516,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>3023</v>
+      <c r="D70" t="n">
+        <v>3616</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>SN-2025-1738-0069</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2538,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>+62-831-5207</t>
+          <t>+62-222-4619</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2896,22 +2546,17 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>1044</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>카카오</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>1280</v>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>SN-2025-1738-0070</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2568,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>+62-428-4678</t>
+          <t>+62-450-7759</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2931,22 +2576,17 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>2057</v>
+      <c r="D72" t="n">
+        <v>4082</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>SN-2025-1738-0071</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2598,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>+62-717-4397</t>
+          <t>+62-995-5014</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2966,34 +2606,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>4168</v>
+      <c r="D73" t="n">
+        <v>2104</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>SN-2025-1738-0072</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Agus</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>+62-756-6273</t>
+          <t>+62-537-5240</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3001,34 +2636,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>3853</v>
+      <c r="D74" t="n">
+        <v>1921</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>SN-2025-1738-0073</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Budi</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>+62-648-1266</t>
+          <t>+62-603-4216</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3036,34 +2666,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>4053</v>
+      <c r="D75" t="n">
+        <v>1129</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>팜유</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>SN-2025-1738-0074</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>+62-163-5698</t>
+          <t>+62-883-1644</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3071,34 +2696,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>4729</v>
+      <c r="D76" t="n">
+        <v>4022</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>SN-2025-1738-0075</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>이영희66</t>
+          <t>이영희4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>010-7233-8281</t>
+          <t>010-4973-8432</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3106,34 +2726,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>배추</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>3213</v>
+      <c r="D77" t="n">
+        <v>1571</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>SN-2025-1738-0076</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>+62-518-2966</t>
+          <t>+62-170-7924</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3141,34 +2756,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>3221</v>
+      <c r="D78" t="n">
+        <v>1775</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>SN-2025-1738-0077</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강호동20</t>
+          <t>박지성73</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>010-2470-7368</t>
+          <t>010-1760-6061</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3176,34 +2786,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>인삼</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>2802</v>
+      <c r="D79" t="n">
+        <v>2655</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>SN-2025-1738-0078</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>박지성23</t>
+          <t>이영희86</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>010-4531-5212</t>
+          <t>010-6319-2051</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3211,22 +2816,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>4065</v>
+      <c r="D80" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>SN-2025-1738-0079</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -3238,7 +2838,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>+84-611-8127</t>
+          <t>+84-259-8096</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3246,34 +2846,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1279</v>
+      <c r="D81" t="n">
+        <v>2565</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>SN-2025-1738-0080</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Siti</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>+62-729-5105</t>
+          <t>+62-157-1329</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3281,34 +2876,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>2570</v>
+      <c r="D82" t="n">
+        <v>1734</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>SN-2025-1738-0081</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>+84-179-4212</t>
+          <t>+84-923-8631</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3316,34 +2906,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>1584</v>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>커피</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>4364</v>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>SN-2025-1738-0082</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>+62-399-9183</t>
+          <t>+62-298-7647</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3351,34 +2936,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>2064</v>
+      <c r="D84" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>SN-2025-1738-0083</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>+84-299-2547</t>
+          <t>+84-929-6142</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3386,34 +2966,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>2831</v>
+      <c r="D85" t="n">
+        <v>3190</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>SN-2025-1738-0084</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>+62-836-3233</t>
+          <t>+62-117-8143</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3421,34 +2996,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>2326</v>
+      <c r="D86" t="n">
+        <v>3731</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>SN-2025-1738-0085</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>+62-480-3728</t>
+          <t>+62-629-6707</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3456,34 +3026,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>옥수수</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>4540</v>
+      <c r="D87" t="n">
+        <v>4843</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>SN-2025-1738-0086</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dewi</t>
+          <t>Budi</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>+62-847-5653</t>
+          <t>+62-644-1542</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3491,34 +3056,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>2226</v>
+      <c r="D88" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>SN-2025-1738-0087</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Eko</t>
+          <t>Dewi</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>+62-665-4009</t>
+          <t>+62-685-9497</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3526,34 +3086,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>4050</v>
+      <c r="D89" t="n">
+        <v>3963</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>카사바</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>SN-2025-1738-0088</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>이영희72</t>
+          <t>강호동98</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>010-3696-1734</t>
+          <t>010-2411-5904</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3561,22 +3116,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>1888</v>
+      <c r="D90" t="n">
+        <v>4804</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>인삼</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>SN-2025-1738-0089</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3138,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>+62-689-5649</t>
+          <t>+62-247-6245</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3596,34 +3146,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>4162</v>
+      <c r="D91" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>SN-2025-1738-0090</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>김철수14</t>
+          <t>김철수62</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>010-8594-9300</t>
+          <t>010-5006-2657</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3631,34 +3176,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>2890</v>
+      <c r="D92" t="n">
+        <v>3355</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>배추</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>SN-2025-1738-0091</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Nguyen Van A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>+84-736-1792</t>
+          <t>+84-812-9417</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3666,34 +3206,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>커피</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>3969</v>
+      <c r="D93" t="n">
+        <v>3089</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>용과</t>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>SN-2025-1738-0092</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Le Van C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>+84-240-1285</t>
+          <t>+84-335-6725</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3701,22 +3236,17 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>고무</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>1791</v>
+      <c r="D94" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>SN-2025-1738-0093</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3258,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>+62-801-2270</t>
+          <t>+62-575-3022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3736,34 +3266,29 @@
           <t>SHIPPING 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>팜유</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1684</v>
+      <c r="D95" t="n">
+        <v>4943</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>SN-2025-1738-0094</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>+84-400-1214</t>
+          <t>+84-549-1874</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3771,34 +3296,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>용과</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>3587</v>
+      <c r="D96" t="n">
+        <v>4866</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>고무</t>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>SN-2025-1738-0095</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Le Van C</t>
+          <t>Pham Van D</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>+84-312-6120</t>
+          <t>+84-169-1563</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3806,34 +3326,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>3371</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>커피</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>1238</v>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>SN-2025-1738-0096</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Siti</t>
+          <t>Eko</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>+62-290-6574</t>
+          <t>+62-100-4824</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3841,34 +3356,29 @@
           <t>INDONESIA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>카사바</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>4046</v>
+      <c r="D98" t="n">
+        <v>4299</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>SN-2025-1738-0097</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>정우성6</t>
+          <t>이영희83</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>010-4755-8940</t>
+          <t>010-2628-4158</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3876,34 +3386,29 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>인삼</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>2673</v>
+      <c r="D99" t="n">
+        <v>2457</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>SN-2025-1738-0098</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pham Van D</t>
+          <t>Tran Thi B</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>+84-323-3690</t>
+          <t>+84-285-3742</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3911,34 +3416,29 @@
           <t>VIETNAM 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>2239</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>용과</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>3152</v>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>SN-2025-1738-0099</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>박지성44</t>
+          <t>김철수35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>010-6250-5556</t>
+          <t>010-6279-2515</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3946,22 +3446,17 @@
           <t>KOREA 지역 상세 주소</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>사과</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>4991</v>
+      <c r="D101" t="n">
+        <v>3325</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>SN-2025-1738-0100</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
         </is>
       </c>
     </row>
